--- a/projetos/OBRA_TMULT/02_ORCAMENTO_BASE_E_CONTRATOS/CONTRATOS_EQUIPAMENTOS/PLANILHA_GESTAO_LOCACAO_EQUIPAMENTOS.xlsx
+++ b/projetos/OBRA_TMULT/02_ORCAMENTO_BASE_E_CONTRATOS/CONTRATOS_EQUIPAMENTOS/PLANILHA_GESTAO_LOCACAO_EQUIPAMENTOS.xlsx
@@ -550,7 +550,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PAINEL DE GESTÃO DE CONTRATOS DE LOCAÇÃO DE EQUIPAMENTOS (OBRA_TMULT - R$ 141.499,98)</t>
+          <t>PAINEL DE GESTÃO DE CONTRATOS DE LOCAÇÃO DE EQUIPAMENTOS (TMULT - R$ 141,899.98)</t>
         </is>
       </c>
     </row>
